--- a/products.xlsx
+++ b/products.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\1042273\Project\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\1042273\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6F3F125-9686-44C7-9510-F9479211BA98}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{713B8036-98BD-4FEC-A97A-7299DA9870FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="41">
   <si>
     <t>name</t>
   </si>
@@ -55,9 +55,6 @@
     <t>6,7,8,9,10</t>
   </si>
   <si>
-    <t>walklite-runner</t>
-  </si>
-  <si>
     <t>Harbor Slip-On</t>
   </si>
   <si>
@@ -143,6 +140,9 @@
   </si>
   <si>
     <t>Rohit WalkLite Runner</t>
+  </si>
+  <si>
+    <t>rohit-walklite-runner</t>
   </si>
 </sst>
 </file>
@@ -482,7 +482,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
@@ -519,7 +519,7 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B2" t="s">
         <v>7</v>
@@ -537,104 +537,104 @@
         <v>10</v>
       </c>
       <c r="G2" t="s">
-        <v>11</v>
+        <v>40</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" t="s">
         <v>12</v>
-      </c>
-      <c r="B3" t="s">
-        <v>13</v>
       </c>
       <c r="C3">
         <v>52</v>
       </c>
       <c r="D3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E3" t="s">
         <v>14</v>
       </c>
-      <c r="E3" t="s">
+      <c r="F3" t="s">
         <v>15</v>
       </c>
-      <c r="F3" t="s">
+      <c r="G3" t="s">
         <v>16</v>
-      </c>
-      <c r="G3" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B4" t="s">
         <v>18</v>
-      </c>
-      <c r="B4" t="s">
-        <v>19</v>
       </c>
       <c r="C4">
         <v>89</v>
       </c>
       <c r="D4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E4" t="s">
         <v>20</v>
       </c>
-      <c r="E4" t="s">
+      <c r="F4" t="s">
         <v>21</v>
       </c>
-      <c r="F4" t="s">
+      <c r="G4" t="s">
         <v>22</v>
-      </c>
-      <c r="G4" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
+        <v>23</v>
+      </c>
+      <c r="B5" t="s">
         <v>24</v>
-      </c>
-      <c r="B5" t="s">
-        <v>25</v>
       </c>
       <c r="C5">
         <v>34</v>
       </c>
       <c r="D5" t="s">
+        <v>25</v>
+      </c>
+      <c r="E5" t="s">
         <v>26</v>
       </c>
-      <c r="E5" t="s">
+      <c r="F5" t="s">
         <v>27</v>
       </c>
-      <c r="F5" t="s">
+      <c r="G5" t="s">
         <v>28</v>
-      </c>
-      <c r="G5" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B6" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C6">
         <v>61</v>
       </c>
       <c r="D6" t="s">
+        <v>30</v>
+      </c>
+      <c r="E6" t="s">
         <v>31</v>
       </c>
-      <c r="E6" t="s">
+      <c r="F6" t="s">
         <v>32</v>
       </c>
-      <c r="F6" t="s">
+      <c r="G6" t="s">
         <v>33</v>
-      </c>
-      <c r="G6" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B7" t="s">
         <v>7</v>
@@ -643,16 +643,154 @@
         <v>74</v>
       </c>
       <c r="D7" t="s">
+        <v>35</v>
+      </c>
+      <c r="E7" t="s">
         <v>36</v>
       </c>
-      <c r="E7" t="s">
+      <c r="F7" t="s">
         <v>37</v>
       </c>
-      <c r="F7" t="s">
+      <c r="G7" t="s">
         <v>38</v>
       </c>
-      <c r="G7" t="s">
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
         <v>39</v>
+      </c>
+      <c r="B8" t="s">
+        <v>7</v>
+      </c>
+      <c r="C8">
+        <v>68</v>
+      </c>
+      <c r="D8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E8" t="s">
+        <v>9</v>
+      </c>
+      <c r="F8" t="s">
+        <v>10</v>
+      </c>
+      <c r="G8" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>11</v>
+      </c>
+      <c r="B9" t="s">
+        <v>12</v>
+      </c>
+      <c r="C9">
+        <v>52</v>
+      </c>
+      <c r="D9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E9" t="s">
+        <v>14</v>
+      </c>
+      <c r="F9" t="s">
+        <v>15</v>
+      </c>
+      <c r="G9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>17</v>
+      </c>
+      <c r="B10" t="s">
+        <v>18</v>
+      </c>
+      <c r="C10">
+        <v>89</v>
+      </c>
+      <c r="D10" t="s">
+        <v>19</v>
+      </c>
+      <c r="E10" t="s">
+        <v>20</v>
+      </c>
+      <c r="F10" t="s">
+        <v>21</v>
+      </c>
+      <c r="G10" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>23</v>
+      </c>
+      <c r="B11" t="s">
+        <v>24</v>
+      </c>
+      <c r="C11">
+        <v>34</v>
+      </c>
+      <c r="D11" t="s">
+        <v>25</v>
+      </c>
+      <c r="E11" t="s">
+        <v>26</v>
+      </c>
+      <c r="F11" t="s">
+        <v>27</v>
+      </c>
+      <c r="G11" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>29</v>
+      </c>
+      <c r="B12" t="s">
+        <v>12</v>
+      </c>
+      <c r="C12">
+        <v>61</v>
+      </c>
+      <c r="D12" t="s">
+        <v>30</v>
+      </c>
+      <c r="E12" t="s">
+        <v>31</v>
+      </c>
+      <c r="F12" t="s">
+        <v>32</v>
+      </c>
+      <c r="G12" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>34</v>
+      </c>
+      <c r="B13" t="s">
+        <v>7</v>
+      </c>
+      <c r="C13">
+        <v>74</v>
+      </c>
+      <c r="D13" t="s">
+        <v>35</v>
+      </c>
+      <c r="E13" t="s">
+        <v>36</v>
+      </c>
+      <c r="F13" t="s">
+        <v>37</v>
+      </c>
+      <c r="G13" t="s">
+        <v>38</v>
       </c>
     </row>
   </sheetData>
